--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484024_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484024_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1306</v>
+        <v>4.3091</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8032</v>
+        <v>4.7012</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6726</v>
+        <v>-0.3921</v>
       </c>
       <c r="G2" t="n">
         <v>2.8848</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4449</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0001</v>
+        <v>-0.1019</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6236</v>
+        <v>-0.343</v>
       </c>
       <c r="V2" t="n">
         <v>1.4724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8617</v>
+        <v>3.9484</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9697</v>
+        <v>5.6636</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.108</v>
+        <v>-1.7152</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2766</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5486</v>
+        <v>-0.462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1135</v>
+        <v>-0.1926</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6621</v>
+        <v>-0.2694</v>
       </c>
       <c r="V3" t="n">
         <v>5.0918</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3057</v>
+        <v>0.5152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7191</v>
+        <v>0.1069</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5866</v>
+        <v>0.4083</v>
       </c>
       <c r="G4" t="n">
         <v>-2.9325</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3771</v>
+        <v>0.5866</v>
       </c>
       <c r="T4" t="n">
-        <v>0.618</v>
+        <v>0.0058</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7591</v>
+        <v>0.5808</v>
       </c>
       <c r="V4" t="n">
         <v>1.4724</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0085</v>
+        <v>-0.6923</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6126</v>
+        <v>-0.4085</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.396</v>
+        <v>-0.2838</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3583</v>
@@ -922,13 +922,13 @@
         <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3843</v>
+        <v>-0.068</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1133</v>
+        <v>0.0907</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.271</v>
+        <v>-0.1587</v>
       </c>
       <c r="V6" t="n">
         <v>0.3373</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1317</v>
+        <v>-1.2975</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1532</v>
+        <v>-2.4593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0216</v>
+        <v>1.1618</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1199</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2182</v>
+        <v>-0.384</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5243</v>
+        <v>-0.3841</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9671</v>
+        <v>-2.3346</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3029</v>
+        <v>-1.8947</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6643</v>
+        <v>-0.4398</v>
       </c>
       <c r="G8" t="n">
         <v>-1.296</v>
@@ -1078,13 +1078,13 @@
         <v>2.7774</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4374</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.3343</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.4706</v>
       </c>
       <c r="V8" t="n">
         <v>2.1469</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3427</v>
+        <v>-3.6005</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1281</v>
+        <v>-2.4139</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2147</v>
+        <v>-1.1866</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9788</v>
@@ -1156,13 +1156,13 @@
         <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6138</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1732</v>
+        <v>-0.459</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4406</v>
+        <v>-0.4125</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9405</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8195000000000014</v>
+        <v>0.8193000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3355</v>
+        <v>3.335599999999999</v>
       </c>
       <c r="F10" t="n">
         <v>-2.5162</v>
@@ -1237,10 +1237,10 @@
         <v>-2.7208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9911999999999999</v>
+        <v>-0.9913</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7297</v>
+        <v>-1.7296</v>
       </c>
       <c r="V10" t="n">
         <v>9.580299999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.7508</v>
+        <v>6.4702</v>
       </c>
       <c r="E11" t="n">
         <v>3.3855</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3653</v>
+        <v>3.0848</v>
       </c>
       <c r="G11" t="n">
         <v>4.9209</v>
@@ -1312,13 +1312,13 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4251</v>
+        <v>0.1445</v>
       </c>
       <c r="T11" t="n">
         <v>-0.306</v>
       </c>
       <c r="U11" t="n">
-        <v>0.731</v>
+        <v>0.4505</v>
       </c>
       <c r="V11" t="n">
         <v>1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0295</v>
+        <v>3.3492</v>
       </c>
       <c r="E12" t="n">
-        <v>2.883</v>
+        <v>3.2911</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1465</v>
+        <v>0.0581</v>
       </c>
       <c r="G12" t="n">
         <v>5.2702</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8819</v>
+        <v>1.2017</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1531</v>
+        <v>0.5613</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7288</v>
+        <v>0.6404</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2129</v>
+        <v>0.1935</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3077</v>
+        <v>0.7975</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0948</v>
+        <v>-0.604</v>
       </c>
       <c r="G13" t="n">
         <v>2.2649</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1544</v>
+        <v>1.135</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0034</v>
+        <v>0.4933</v>
       </c>
       <c r="U13" t="n">
-        <v>1.151</v>
+        <v>0.6418</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4129</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7805</v>
+        <v>-0.6897</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8791</v>
+        <v>0.9317</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9013</v>
+        <v>-1.6214</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1325</v>
+        <v>1.3255</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4486</v>
+        <v>1.3812</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3162</v>
+        <v>-0.0557</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2317</v>
+        <v>2.2815</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0711</v>
+        <v>2.2337</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1606</v>
+        <v>0.0478</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3642</v>
+        <v>-0.956</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.8525</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1555</v>
+        <v>-0.1035</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0448</v>
+        <v>0.3302</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1189</v>
+        <v>0.1021</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0742</v>
+        <v>0.228</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2065</v>
+        <v>-2.1469</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8945</v>
+        <v>-1.244</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1155</v>
+        <v>-0.6751</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.01</v>
+        <v>-0.5689</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3255</v>
+        <v>-0.1325</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3812</v>
+        <v>-0.4486</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0557</v>
+        <v>0.3162</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2815</v>
+        <v>0.2317</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2337</v>
+        <v>0.0711</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0478</v>
+        <v>0.1606</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.956</v>
+        <v>-0.3642</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8525</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1035</v>
+        <v>0.1555</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8746</v>
+        <v>0.4917</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7141</v>
+        <v>0.0851</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1605</v>
+        <v>0.4066</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1469</v>
+        <v>-1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0007</v>
+        <v>-1.9922</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7186</v>
+        <v>-1.1267</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2821</v>
+        <v>-0.8655</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5113</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3798</v>
+        <v>0.3883</v>
       </c>
       <c r="T16" t="n">
-        <v>1.009</v>
+        <v>0.6009</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6292</v>
+        <v>-0.2126</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8692</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2446</v>
+        <v>-2.8593</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0095</v>
+        <v>-2.9561</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2351</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.876</v>
+        <v>-2.2296</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2619</v>
+        <v>-1.0429</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.614</v>
+        <v>-1.1867</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6874</v>
+        <v>-1.6015</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7276</v>
+        <v>-0.9264</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>-0.6751</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1886</v>
+        <v>-0.6281</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5344</v>
+        <v>-0.1165</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6542</v>
+        <v>-0.5117</v>
       </c>
       <c r="P17" t="n">
         <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4454</v>
+        <v>-0.6135</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6779</v>
+        <v>-0.3626</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2324</v>
+        <v>-0.2509</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.0044</v>
+        <v>-1.2065</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.0044</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8923</v>
+        <v>-3.367</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5682</v>
+        <v>-1.1319</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3241</v>
+        <v>-2.2351</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2296</v>
+        <v>-2.876</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0429</v>
+        <v>-2.2619</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1867</v>
+        <v>-0.614</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6015</v>
+        <v>-1.6874</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9264</v>
+        <v>-1.7276</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6751</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6281</v>
+        <v>-1.1886</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1165</v>
+        <v>-0.5344</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5117</v>
+        <v>-0.6542</v>
       </c>
       <c r="P18" t="n">
         <v>1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6465</v>
+        <v>0.3231</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9748</v>
+        <v>0.5555</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6717</v>
+        <v>-0.2324</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>-2.0044</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-2.0044</v>
       </c>
     </row>
     <row r="19">
@@ -1891,16 +1891,16 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8193999999999999</v>
+        <v>-0.1393000000000004</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5163</v>
+        <v>2.516000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3356</v>
+        <v>-2.6553</v>
       </c>
       <c r="G19" t="n">
-        <v>7.032099999999999</v>
+        <v>7.032099999999998</v>
       </c>
       <c r="H19" t="n">
         <v>2.270899999999999</v>
@@ -1927,7 +1927,7 @@
         <v>-1.133</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9919000000000002</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q19" t="n">
         <v>-13.8868</v>
@@ -1936,16 +1936,16 @@
         <v>12.895</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7207</v>
+        <v>3.401</v>
       </c>
       <c r="T19" t="n">
         <v>1.7296</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9912000000000001</v>
+        <v>1.6714</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.580399999999999</v>
+        <v>-9.580400000000001</v>
       </c>
       <c r="W19" t="n">
         <v>2.2705</v>
